--- a/OPA/data/OPA.xlsx
+++ b/OPA/data/OPA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>Linse</t>
   </si>
@@ -110,13 +110,19 @@
     <t>Linse links (cm)</t>
   </si>
   <si>
-    <t>Bild links (cm)</t>
+    <t>Größe links (cm)</t>
+  </si>
+  <si>
+    <t>Anzahl links</t>
   </si>
   <si>
     <t>Linse rechts (cm)</t>
   </si>
   <si>
     <t>Bild rechts (mm)</t>
+  </si>
+  <si>
+    <t>Anzahl rechts</t>
   </si>
 </sst>
 </file>
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -178,6 +184,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -942,6 +951,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="17.63"/>
+    <col customWidth="1" min="5" max="5" width="17.38"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
@@ -959,6 +972,12 @@
       <c r="E1" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5">
@@ -970,8 +989,11 @@
       <c r="C2" s="5">
         <v>3.9</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="6">
+        <v>1.0</v>
+      </c>
       <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="5">
@@ -983,8 +1005,11 @@
       <c r="C3" s="5">
         <v>3.7</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="6">
+        <v>1.0</v>
+      </c>
       <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="5">
@@ -996,8 +1021,11 @@
       <c r="C4" s="5">
         <v>3.5</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="6">
+        <v>1.0</v>
+      </c>
       <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="5">
@@ -1009,8 +1037,11 @@
       <c r="C5" s="5">
         <v>3.3</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="6">
+        <v>1.0</v>
+      </c>
       <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="5">
@@ -1022,8 +1053,11 @@
       <c r="C6" s="5">
         <v>3.1</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="6">
+        <v>1.0</v>
+      </c>
       <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="5">
@@ -1035,11 +1069,17 @@
       <c r="C7" s="5">
         <v>2.8</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E7" s="5">
         <v>106.5</v>
       </c>
-      <c r="E7" s="5">
-        <v>1.5</v>
+      <c r="F7" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -1052,11 +1092,17 @@
       <c r="C8" s="5">
         <v>2.7</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="5">
         <v>101.2</v>
       </c>
-      <c r="E8" s="5">
-        <v>1.0</v>
+      <c r="F8" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="9">
@@ -1069,11 +1115,17 @@
       <c r="C9" s="5">
         <v>2.5</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="5">
         <v>90.3</v>
       </c>
-      <c r="E9" s="5">
-        <v>1.0</v>
+      <c r="F9" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="10">
@@ -1086,11 +1138,17 @@
       <c r="C10" s="5">
         <v>2.2</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="5">
         <v>80.8</v>
       </c>
-      <c r="E10" s="5">
-        <v>1.2</v>
+      <c r="F10" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="11">
@@ -1103,11 +1161,17 @@
       <c r="C11" s="5">
         <v>2.1</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="5">
         <v>85.6</v>
       </c>
-      <c r="E11" s="5">
-        <v>1.4</v>
+      <c r="F11" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="12">
@@ -1120,11 +1184,17 @@
       <c r="C12" s="5">
         <v>1.8</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="5">
         <v>80.2</v>
       </c>
-      <c r="E12" s="5">
-        <v>1.4</v>
+      <c r="F12" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="13">
@@ -1137,11 +1207,17 @@
       <c r="C13" s="5">
         <v>1.6</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="5">
         <v>75.3</v>
       </c>
-      <c r="E13" s="5">
-        <v>1.6</v>
+      <c r="F13" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="14">
@@ -1151,14 +1227,20 @@
       <c r="B14" s="5">
         <v>37.7</v>
       </c>
-      <c r="C14" s="5">
-        <v>1.43</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E14" s="5">
         <v>65.5</v>
       </c>
-      <c r="E14" s="5">
-        <v>1.8</v>
+      <c r="F14" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="15">
@@ -1168,14 +1250,20 @@
       <c r="B15" s="5">
         <v>38.4</v>
       </c>
-      <c r="C15" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="D15" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E15" s="5">
         <v>64.0</v>
       </c>
-      <c r="E15" s="5">
-        <v>2.0</v>
+      <c r="F15" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="16">
@@ -1185,14 +1273,20 @@
       <c r="B16" s="5">
         <v>39.4</v>
       </c>
-      <c r="C16" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="E16" s="5">
         <v>56.5</v>
       </c>
-      <c r="E16" s="5">
-        <v>2.8</v>
+      <c r="F16" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>

--- a/OPA/data/OPA.xlsx
+++ b/OPA/data/OPA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>Linse</t>
   </si>
@@ -102,6 +102,42 @@
   </si>
   <si>
     <t>Abstand G-E 3cm</t>
+  </si>
+  <si>
+    <t>messung 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">messung 2 gedereht </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bessel methode </t>
+  </si>
+  <si>
+    <t>gegenstandsabstand</t>
+  </si>
+  <si>
+    <t>330mm</t>
+  </si>
+  <si>
+    <t>E-G-Spiegel</t>
+  </si>
+  <si>
+    <t>schirm 1000mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Messung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">linke psoition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rechte psotion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeweils position der llinken linse E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linse wird bewegt </t>
   </si>
   <si>
     <t>Pos. Schirm [cm]</t>
@@ -940,6 +976,105 @@
         <v>33.4</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46.8</v>
+      </c>
+      <c r="C17" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>75.2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46.8</v>
+      </c>
+      <c r="C19" s="2">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46.9</v>
+      </c>
+      <c r="C20" s="2">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46.9</v>
+      </c>
+      <c r="C21" s="2">
+        <v>74.9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -958,25 +1093,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">

--- a/OPA/data/OPA.xlsx
+++ b/OPA/data/OPA.xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henribreuer/Programmieren/Python/AP3/OPA/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35BCB00-56ED-FE49-B093-F07C00F905A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="A1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="A2" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="A3" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="A4" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="A5" sheetId="5" r:id="rId9"/>
+    <sheet name="A1" sheetId="1" r:id="rId1"/>
+    <sheet name="A2" sheetId="2" r:id="rId2"/>
+    <sheet name="A3" sheetId="3" r:id="rId3"/>
+    <sheet name="A4" sheetId="4" r:id="rId4"/>
+    <sheet name="A5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>Linse</t>
   </si>
@@ -104,51 +113,12 @@
     <t>Abstand G-E 3cm</t>
   </si>
   <si>
-    <t>messung 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">messung 2 gedereht </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bessel methode </t>
-  </si>
-  <si>
-    <t>gegenstandsabstand</t>
-  </si>
-  <si>
-    <t>330mm</t>
-  </si>
-  <si>
-    <t>E-G-Spiegel</t>
-  </si>
-  <si>
-    <t>schirm 1000mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messung </t>
-  </si>
-  <si>
-    <t xml:space="preserve">linke psoition </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rechte psotion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jeweils position der llinken linse E </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linse wird bewegt </t>
-  </si>
-  <si>
     <t>Pos. Schirm [cm]</t>
   </si>
   <si>
     <t>Linse links (cm)</t>
   </si>
   <si>
-    <t>Größe links (cm)</t>
-  </si>
-  <si>
     <t>Anzahl links</t>
   </si>
   <si>
@@ -159,33 +129,42 @@
   </si>
   <si>
     <t>Anzahl rechts</t>
+  </si>
+  <si>
+    <t>Bild links (cm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -193,71 +172,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -447,17 +403,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -473,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -481,7 +440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -489,7 +448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -505,7 +464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -514,22 +473,23 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="19.25"/>
-    <col customWidth="1" min="6" max="6" width="26.0"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,163 +506,164 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>34.8</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="D3" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
         <v>34.9</v>
       </c>
       <c r="D4" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>34.9</v>
       </c>
       <c r="D5" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2">
         <v>37.9</v>
       </c>
       <c r="D8" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2">
         <v>37.6</v>
       </c>
       <c r="D9" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2">
         <v>37.6</v>
       </c>
       <c r="D10" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2">
         <v>37.5</v>
       </c>
       <c r="D11" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2">
         <v>37.6</v>
       </c>
       <c r="D12" s="2">
-        <v>45.0</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="22.13"/>
-    <col customWidth="1" min="4" max="4" width="23.75"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -719,46 +680,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
         <v>51.1</v>
       </c>
       <c r="D2" s="2">
-        <v>64.4</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2">
-        <v>64.4</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
         <v>50.9</v>
@@ -767,12 +728,12 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>50.6</v>
@@ -781,32 +742,32 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>50.7</v>
       </c>
       <c r="D6" s="2">
-        <v>64.9</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2">
         <v>54.2</v>
@@ -818,15 +779,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2">
         <v>76.7</v>
@@ -835,12 +796,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2">
         <v>53.9</v>
@@ -849,12 +810,12 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2">
         <v>54.2</v>
@@ -863,36 +824,37 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2">
         <v>76.3</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="31.88"/>
+    <col min="5" max="5" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -906,15 +868,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>47.7</v>
       </c>
       <c r="C2" s="2">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>24</v>
@@ -923,9 +885,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>47.8</v>
@@ -940,9 +902,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>47.8</v>
@@ -954,9 +916,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>47.6</v>
@@ -965,9 +927,9 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>47.4</v>
@@ -976,455 +938,352 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46.8</v>
-      </c>
-      <c r="C17" s="2">
-        <v>75.0</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B18" s="2">
-        <v>47.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>75.2</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B19" s="2">
-        <v>46.8</v>
-      </c>
-      <c r="C19" s="2">
-        <v>75.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46.9</v>
-      </c>
-      <c r="C20" s="2">
-        <v>75.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B21" s="2">
-        <v>46.9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>74.9</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="17.63"/>
-    <col customWidth="1" min="5" max="5" width="17.38"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5">
-        <v>145.0</v>
-      </c>
-      <c r="B2" s="5">
-        <v>34.2</v>
-      </c>
-      <c r="C2" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4">
+        <v>145</v>
+      </c>
+      <c r="B2" s="4">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="C2" s="4">
         <v>3.9</v>
       </c>
-      <c r="D2" s="6">
-        <v>1.0</v>
+      <c r="D2" s="4">
+        <v>1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3">
-      <c r="A3" s="5">
-        <v>140.0</v>
-      </c>
-      <c r="B3" s="5">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4">
+        <v>140</v>
+      </c>
+      <c r="B3" s="4">
         <v>34.4</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>3.7</v>
       </c>
-      <c r="D3" s="6">
-        <v>1.0</v>
+      <c r="D3" s="4">
+        <v>1</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4">
-      <c r="A4" s="5">
-        <v>135.0</v>
-      </c>
-      <c r="B4" s="5">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4">
+        <v>135</v>
+      </c>
+      <c r="B4" s="4">
         <v>34.4</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>3.5</v>
       </c>
-      <c r="D4" s="6">
-        <v>1.0</v>
+      <c r="D4" s="4">
+        <v>1</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5">
-      <c r="A5" s="5">
-        <v>130.0</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4">
+        <v>130</v>
+      </c>
+      <c r="B5" s="4">
         <v>34.5</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>3.3</v>
       </c>
-      <c r="D5" s="6">
-        <v>1.0</v>
+      <c r="D5" s="4">
+        <v>1</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6">
-      <c r="A6" s="5">
-        <v>125.0</v>
-      </c>
-      <c r="B6" s="5">
-        <v>34.7</v>
-      </c>
-      <c r="C6" s="5">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4">
+        <v>125</v>
+      </c>
+      <c r="B6" s="4">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="C6" s="4">
         <v>3.1</v>
       </c>
-      <c r="D6" s="6">
-        <v>1.0</v>
+      <c r="D6" s="4">
+        <v>1</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7">
-      <c r="A7" s="5">
-        <v>120.0</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4">
+        <v>120</v>
+      </c>
+      <c r="B7" s="4">
         <v>34.9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>2.8</v>
       </c>
-      <c r="D7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E7" s="5">
-        <v>106.5</v>
-      </c>
-      <c r="F7" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5">
-        <v>115.0</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4">
+        <v>115</v>
+      </c>
+      <c r="B8" s="4">
         <v>34.9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>2.7</v>
       </c>
-      <c r="D8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
         <v>101.2</v>
       </c>
-      <c r="F8" s="6">
-        <v>3.0</v>
+      <c r="F8" s="4">
+        <v>3</v>
       </c>
       <c r="G8" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4">
+        <v>110</v>
+      </c>
+      <c r="B9" s="4">
         <v>35.5</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>2.5</v>
       </c>
-      <c r="D9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
         <v>90.3</v>
       </c>
-      <c r="F9" s="6">
-        <v>5.0</v>
+      <c r="F9" s="4">
+        <v>5</v>
       </c>
       <c r="G9" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5">
-        <v>105.0</v>
-      </c>
-      <c r="B10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4">
+        <v>105</v>
+      </c>
+      <c r="B10" s="4">
         <v>35.4</v>
       </c>
-      <c r="C10" s="5">
-        <v>2.2</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="C10" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
         <v>80.8</v>
       </c>
-      <c r="F10" s="6">
-        <v>6.0</v>
+      <c r="F10" s="4">
+        <v>6</v>
       </c>
       <c r="G10" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="B11" s="5">
-        <v>35.7</v>
-      </c>
-      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4">
+        <v>100</v>
+      </c>
+      <c r="B11" s="4">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="C11" s="4">
         <v>2.1</v>
       </c>
-      <c r="D11" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
         <v>85.6</v>
       </c>
-      <c r="F11" s="6">
-        <v>7.0</v>
+      <c r="F11" s="4">
+        <v>7</v>
       </c>
       <c r="G11" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5">
-        <v>95.0</v>
-      </c>
-      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4">
+        <v>95</v>
+      </c>
+      <c r="B12" s="4">
         <v>36.4</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>1.8</v>
       </c>
-      <c r="D12" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
         <v>80.2</v>
       </c>
-      <c r="F12" s="6">
-        <v>7.0</v>
+      <c r="F12" s="4">
+        <v>7</v>
       </c>
       <c r="G12" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5">
-        <v>90.0</v>
-      </c>
-      <c r="B13" s="5">
-        <v>37.0</v>
-      </c>
-      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="4">
+        <v>90</v>
+      </c>
+      <c r="B13" s="4">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4">
         <v>1.6</v>
       </c>
-      <c r="D13" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
         <v>75.3</v>
       </c>
-      <c r="F13" s="6">
-        <v>8.0</v>
+      <c r="F13" s="4">
+        <v>8</v>
       </c>
       <c r="G13" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5">
-        <v>85.0</v>
-      </c>
-      <c r="B14" s="5">
-        <v>37.7</v>
-      </c>
-      <c r="C14" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="C14" s="4">
         <v>4.3</v>
       </c>
-      <c r="D14" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
         <v>65.5</v>
       </c>
-      <c r="F14" s="6">
-        <v>9.0</v>
+      <c r="F14" s="4">
+        <v>9</v>
       </c>
       <c r="G14" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <v>80.0</v>
-      </c>
-      <c r="B15" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="4">
+        <v>80</v>
+      </c>
+      <c r="B15" s="4">
         <v>38.4</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>3.6</v>
       </c>
-      <c r="D15" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>64.0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>10.0</v>
+      <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
+        <v>64</v>
+      </c>
+      <c r="F15" s="4">
+        <v>10</v>
       </c>
       <c r="G15" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>75.0</v>
-      </c>
-      <c r="B16" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="4">
+        <v>75</v>
+      </c>
+      <c r="B16" s="4">
         <v>39.4</v>
       </c>
-      <c r="C16" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="C16" s="4">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
         <v>56.5</v>
       </c>
-      <c r="F16" s="6">
-        <v>15.0</v>
+      <c r="F16" s="4">
+        <v>15</v>
       </c>
       <c r="G16" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>